--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED03.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED03.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:52+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>206W</t>
+          <t>219W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L3"/>
+  <dimension ref="B2:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1697,6 +1697,116 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SIM_XA_FIXED-2-0149</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>141W</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已交</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>第2年</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5季</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3季</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>第3年2季</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SIM_XA_FIXED-4-0134</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>64W</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已交</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>第4年</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5季</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1季</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>第4年3季</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:L2"/>
@@ -1711,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G44"/>
+  <dimension ref="B2:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2031,10 +2141,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="n">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2153,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2170,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2086,7 +2196,7 @@
         <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2112,7 +2222,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2131,14 +2241,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E18" t="n">
-        <v>432</v>
+        <v>390</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2147,7 +2257,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2157,14 +2267,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-15</v>
+        <v>-32</v>
       </c>
       <c r="E19" t="n">
-        <v>417</v>
+        <v>358</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2173,7 +2283,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-8b132cbead"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-9c7ff17ecb", "line_id": "L-8b132cbead", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2183,14 +2293,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E20" t="n">
-        <v>417</v>
+        <v>344</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2199,7 +2309,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-8b132cbead", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2209,14 +2319,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E21" t="n">
-        <v>417</v>
+        <v>329</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2225,7 +2335,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-8b132cbead", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-8b132cbead"}</t>
         </is>
       </c>
     </row>
@@ -2235,23 +2345,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>413</v>
+        <v>329</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-8b132cbead", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2261,23 +2371,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-8b132cbead", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2287,23 +2397,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E24" t="n">
-        <v>385</v>
+        <v>317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2320,11 +2430,11 @@
         <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2339,23 +2449,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>357</v>
+        <v>303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0149", "receivable_term_quarters": 3, "revenue_wan": 141.0}</t>
         </is>
       </c>
     </row>
@@ -2365,23 +2475,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-15</v>
+        <v>-48</v>
       </c>
       <c r="E27" t="n">
-        <v>342</v>
+        <v>255</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-8b132cbead"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2391,23 +2501,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="E28" t="n">
-        <v>342</v>
+        <v>223</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-8b132cbead", "asset_type": "factory"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-8daabb8adc", "line_id": "L-8b132cbead", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2417,23 +2527,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E29" t="n">
-        <v>342</v>
+        <v>209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-8b132cbead", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2443,23 +2553,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>338</v>
+        <v>195</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2476,11 +2586,11 @@
         <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>324</v>
+        <v>181</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2495,23 +2605,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-14</v>
+        <v>141</v>
       </c>
       <c r="E32" t="n">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-024d8d8a90"}</t>
         </is>
       </c>
     </row>
@@ -2521,23 +2631,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E33" t="n">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-8b132cbead"}</t>
         </is>
       </c>
     </row>
@@ -2547,23 +2657,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-8b132cbead", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2573,23 +2683,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>267</v>
+        <v>307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-8b132cbead"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-8b132cbead", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2599,23 +2709,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E36" t="n">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-8b132cbead", "asset_type": "factory"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2625,23 +2735,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-8b132cbead", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2651,23 +2761,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2677,23 +2787,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0134", "receivable_term_quarters": 1, "revenue_wan": 64.0}</t>
         </is>
       </c>
     </row>
@@ -2710,11 +2820,11 @@
         <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2729,23 +2839,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-14</v>
+        <v>64</v>
       </c>
       <c r="E41" t="n">
-        <v>221</v>
+        <v>317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-b795b298ba"}</t>
         </is>
       </c>
     </row>
@@ -2755,23 +2865,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E42" t="n">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-8b132cbead"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2781,23 +2891,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E43" t="n">
-        <v>206</v>
+        <v>288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-8b132cbead", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-8b132cbead"}</t>
         </is>
       </c>
     </row>
@@ -2814,14 +2924,222 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>206</v>
+        <v>288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>第4年4季</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-8b132cbead", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>42</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>288</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>第4年4季</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-8b132cbead", "asset_type": "production_line"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>43</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pay_AD</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E46" t="n">
+        <v>276</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>第5年1季</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>44</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E47" t="n">
+        <v>262</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>第5年1季</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E48" t="n">
+        <v>248</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>第5年2季</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E49" t="n">
+        <v>234</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>第5年3季</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pay_Maintenance</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E50" t="n">
+        <v>219</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>第5年4季</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>maintenance_expense | {"line_id": "L-8b132cbead"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>219</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-8b132cbead", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>219</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-8b132cbead", "asset_type": "production_line"}</t>
         </is>
@@ -2928,16 +3246,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3153,16 +3471,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -3218,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3243,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3268,10 +3586,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3290,16 +3608,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3315,16 +3633,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-75</v>
+        <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-75</v>
+        <v>-22</v>
       </c>
       <c r="G20" t="n">
-        <v>-75</v>
+        <v>-59</v>
       </c>
       <c r="H20" t="n">
-        <v>-61</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="21">
@@ -3365,16 +3683,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-90.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-90.2</v>
+        <v>-37.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-90.2</v>
+        <v>-74.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-76.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="23">
@@ -3415,16 +3733,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-90.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-90.2</v>
+        <v>-37.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-90.2</v>
+        <v>-74.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-76.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="25">
@@ -3465,16 +3783,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-90.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-90.2</v>
+        <v>-37.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-90.2</v>
+        <v>-74.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-76.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="28">
@@ -3564,16 +3882,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>417</v>
+        <v>329</v>
       </c>
       <c r="F30" t="n">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="G30" t="n">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="H30" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31">
@@ -3614,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3642,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -3689,16 +4007,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="F35" t="n">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="G35" t="n">
-        <v>267</v>
+        <v>328</v>
       </c>
       <c r="H35" t="n">
-        <v>206</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36">
@@ -3814,16 +4132,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>498.6</v>
+        <v>490.6</v>
       </c>
       <c r="F40" t="n">
-        <v>408.4</v>
+        <v>453.4</v>
       </c>
       <c r="G40" t="n">
-        <v>318.2</v>
+        <v>379.2</v>
       </c>
       <c r="H40" t="n">
-        <v>242</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41">
@@ -3992,13 +4310,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-176.4</v>
+        <v>-184.4000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>-266.6</v>
+        <v>-221.6000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>-356.8</v>
+        <v>-295.8000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -4014,16 +4332,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-90.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-90.2</v>
+        <v>-37.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-90.2</v>
+        <v>-74.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-76.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="49">
@@ -4039,16 +4357,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>498.6</v>
+        <v>490.6</v>
       </c>
       <c r="F49" t="n">
-        <v>408.4</v>
+        <v>453.3999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>318.2</v>
+        <v>379.1999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>242</v>
+        <v>294.9999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4064,16 +4382,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>498.6</v>
+        <v>490.6</v>
       </c>
       <c r="F50" t="n">
-        <v>408.4</v>
+        <v>453.3999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>318.2</v>
+        <v>379.1999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>242</v>
+        <v>294.9999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4144,7 +4462,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4293,7 +4611,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4442,7 +4760,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4591,7 +4909,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -4740,7 +5058,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
